--- a/backend/Rwanda/technoeconomic-inputs-{model}.xlsx
+++ b/backend/Rwanda/technoeconomic-inputs-{model}.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/{templates}/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="37" documentId="6_{0E28AF21-1CE2-4A91-9061-FE1E52D24DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23E31B1B-8B7F-4242-A78D-37423AF2CD5E}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="6_{0E28AF21-1CE2-4A91-9061-FE1E52D24DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23AE7007-21B2-43ED-93AD-134665CC1402}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Electricity" sheetId="2" r:id="rId1"/>
@@ -37,12 +37,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="18">
   <si>
     <t>Units</t>
-  </si>
-  <si>
-    <t>Baseline</t>
   </si>
   <si>
     <t>Inputs</t>
@@ -274,6 +271,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -548,16 +549,16 @@
   <sheetData>
     <row r="1" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>1</v>
+      <c r="D1" s="4">
+        <v>2020</v>
       </c>
       <c r="E1" s="4">
         <v>2021</v>
@@ -682,13 +683,13 @@
     </row>
     <row r="2" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D2" s="8">
         <v>0</v>
@@ -816,13 +817,13 @@
     </row>
     <row r="3" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3" s="8">
         <v>0</v>
@@ -950,147 +951,147 @@
     </row>
     <row r="4" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="C5" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" s="8">
         <v>0</v>
@@ -1218,13 +1219,13 @@
     </row>
     <row r="6" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="8">
         <v>0</v>
@@ -1352,13 +1353,13 @@
     </row>
     <row r="7" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" s="8">
         <v>0</v>
@@ -1486,147 +1487,147 @@
     </row>
     <row r="8" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" s="10">
         <v>0</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D9" s="8">
         <v>0</v>
@@ -1754,13 +1755,13 @@
     </row>
     <row r="10" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D10" s="8">
         <v>0</v>
@@ -1888,147 +1889,147 @@
     </row>
     <row r="11" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR11" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" s="8">
         <v>0</v>
@@ -2156,13 +2157,13 @@
     </row>
     <row r="13" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" s="8">
         <v>0</v>
@@ -2290,13 +2291,13 @@
     </row>
     <row r="14" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" s="8">
         <v>0</v>
@@ -2424,136 +2425,136 @@
     </row>
     <row r="15" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" s="10">
         <v>0</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR15" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2572,13 +2573,13 @@
   <sheetData>
     <row r="1" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>1</v>
+      <c r="C1" s="4">
+        <v>2020</v>
       </c>
       <c r="D1" s="4">
         <v>2021</v>
@@ -2703,10 +2704,10 @@
     </row>
     <row r="2" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2" s="8">
         <v>0</v>
@@ -2834,10 +2835,10 @@
     </row>
     <row r="3" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="8">
         <v>0</v>
@@ -2965,141 +2966,141 @@
     </row>
     <row r="4" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ4" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="8">
         <v>0</v>
@@ -3227,10 +3228,10 @@
     </row>
     <row r="6" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="8">
         <v>0</v>
@@ -3358,10 +3359,10 @@
     </row>
     <row r="7" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" s="8">
         <v>0</v>
@@ -3489,133 +3490,133 @@
     </row>
     <row r="8" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" s="10">
         <v>0</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ8" s="10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/backend/Rwanda/technoeconomic-inputs-{model}.xlsx
+++ b/backend/Rwanda/technoeconomic-inputs-{model}.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/{templates}/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/Rwanda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="39" documentId="6_{0E28AF21-1CE2-4A91-9061-FE1E52D24DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23AE7007-21B2-43ED-93AD-134665CC1402}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="6_{0E28AF21-1CE2-4A91-9061-FE1E52D24DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFB64C31-7283-4BF6-8420-19366F67B74D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="18">
   <si>
     <t>Units</t>
   </si>
@@ -271,10 +271,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1498,125 +1494,125 @@
       <c r="D8" s="10">
         <v>0</v>
       </c>
-      <c r="E8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="J8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="K8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="L8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="M8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="N8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="O8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="P8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="R8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="S8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="T8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="U8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="V8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="W8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="X8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AP8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AQ8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AR8" s="10" t="s">
-        <v>4</v>
+      <c r="E8" s="10">
+        <v>0</v>
+      </c>
+      <c r="F8" s="10">
+        <v>0</v>
+      </c>
+      <c r="G8" s="10">
+        <v>0</v>
+      </c>
+      <c r="H8" s="10">
+        <v>0</v>
+      </c>
+      <c r="I8" s="10">
+        <v>0</v>
+      </c>
+      <c r="J8" s="10">
+        <v>0</v>
+      </c>
+      <c r="K8" s="10">
+        <v>0</v>
+      </c>
+      <c r="L8" s="10">
+        <v>0</v>
+      </c>
+      <c r="M8" s="10">
+        <v>0</v>
+      </c>
+      <c r="N8" s="10">
+        <v>0</v>
+      </c>
+      <c r="O8" s="10">
+        <v>0</v>
+      </c>
+      <c r="P8" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="10">
+        <v>0</v>
+      </c>
+      <c r="R8" s="10">
+        <v>0</v>
+      </c>
+      <c r="S8" s="10">
+        <v>0</v>
+      </c>
+      <c r="T8" s="10">
+        <v>0</v>
+      </c>
+      <c r="U8" s="10">
+        <v>0</v>
+      </c>
+      <c r="V8" s="10">
+        <v>0</v>
+      </c>
+      <c r="W8" s="10">
+        <v>0</v>
+      </c>
+      <c r="X8" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR8" s="10">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
@@ -2436,125 +2432,125 @@
       <c r="D15" s="10">
         <v>0</v>
       </c>
-      <c r="E15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="I15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="J15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="K15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="L15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="M15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="N15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="O15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="P15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="R15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="S15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="T15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="U15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="V15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="W15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="X15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AP15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AQ15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AR15" s="10" t="s">
-        <v>4</v>
+      <c r="E15" s="10">
+        <v>0</v>
+      </c>
+      <c r="F15" s="10">
+        <v>0</v>
+      </c>
+      <c r="G15" s="10">
+        <v>0</v>
+      </c>
+      <c r="H15" s="10">
+        <v>0</v>
+      </c>
+      <c r="I15" s="10">
+        <v>0</v>
+      </c>
+      <c r="J15" s="10">
+        <v>0</v>
+      </c>
+      <c r="K15" s="10">
+        <v>0</v>
+      </c>
+      <c r="L15" s="10">
+        <v>0</v>
+      </c>
+      <c r="M15" s="10">
+        <v>0</v>
+      </c>
+      <c r="N15" s="10">
+        <v>0</v>
+      </c>
+      <c r="O15" s="10">
+        <v>0</v>
+      </c>
+      <c r="P15" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="10">
+        <v>0</v>
+      </c>
+      <c r="R15" s="10">
+        <v>0</v>
+      </c>
+      <c r="S15" s="10">
+        <v>0</v>
+      </c>
+      <c r="T15" s="10">
+        <v>0</v>
+      </c>
+      <c r="U15" s="10">
+        <v>0</v>
+      </c>
+      <c r="V15" s="10">
+        <v>0</v>
+      </c>
+      <c r="W15" s="10">
+        <v>0</v>
+      </c>
+      <c r="X15" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR15" s="10">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3498,125 +3494,125 @@
       <c r="C8" s="10">
         <v>0</v>
       </c>
-      <c r="D8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="J8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="K8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="L8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="M8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="N8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="O8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="P8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="R8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="S8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="T8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="U8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="V8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="W8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="X8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AP8" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="AQ8" s="10" t="s">
-        <v>4</v>
+      <c r="D8" s="10">
+        <v>0</v>
+      </c>
+      <c r="E8" s="10">
+        <v>0</v>
+      </c>
+      <c r="F8" s="10">
+        <v>0</v>
+      </c>
+      <c r="G8" s="10">
+        <v>0</v>
+      </c>
+      <c r="H8" s="10">
+        <v>0</v>
+      </c>
+      <c r="I8" s="10">
+        <v>0</v>
+      </c>
+      <c r="J8" s="10">
+        <v>0</v>
+      </c>
+      <c r="K8" s="10">
+        <v>0</v>
+      </c>
+      <c r="L8" s="10">
+        <v>0</v>
+      </c>
+      <c r="M8" s="10">
+        <v>0</v>
+      </c>
+      <c r="N8" s="10">
+        <v>0</v>
+      </c>
+      <c r="O8" s="10">
+        <v>0</v>
+      </c>
+      <c r="P8" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="10">
+        <v>0</v>
+      </c>
+      <c r="R8" s="10">
+        <v>0</v>
+      </c>
+      <c r="S8" s="10">
+        <v>0</v>
+      </c>
+      <c r="T8" s="10">
+        <v>0</v>
+      </c>
+      <c r="U8" s="10">
+        <v>0</v>
+      </c>
+      <c r="V8" s="10">
+        <v>0</v>
+      </c>
+      <c r="W8" s="10">
+        <v>0</v>
+      </c>
+      <c r="X8" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="10">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/backend/Rwanda/technoeconomic-inputs-{model}.xlsx
+++ b/backend/Rwanda/technoeconomic-inputs-{model}.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/Rwanda/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/{templates}/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="6_{0E28AF21-1CE2-4A91-9061-FE1E52D24DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFB64C31-7283-4BF6-8420-19366F67B74D}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="6_{0E28AF21-1CE2-4A91-9061-FE1E52D24DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEA536E1-4A58-4C9B-AB49-7F993DF01835}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Electricity" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="16">
   <si>
     <t>Units</t>
   </si>
@@ -63,13 +63,7 @@
     <t>Outputs</t>
   </si>
   <si>
-    <t>Tariff</t>
-  </si>
-  <si>
     <t>Demand</t>
-  </si>
-  <si>
-    <t>$/kWh</t>
   </si>
   <si>
     <t>kWh</t>
@@ -537,15 +531,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99682AE1-5334-4A99-9652-64DF807A4E7D}">
   <sheetPr codeName="Hoja2"/>
-  <dimension ref="A1:AR15"/>
+  <dimension ref="A1:AR13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="44.36328125" customWidth="1"/>
+    <col min="1" max="1" width="16.54296875" customWidth="1"/>
+    <col min="2" max="2" width="25.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>1</v>
@@ -679,13 +674,13 @@
     </row>
     <row r="2" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="8">
         <v>0</v>
@@ -812,279 +807,279 @@
       </c>
     </row>
     <row r="3" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>9</v>
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0</v>
-      </c>
-      <c r="E3" s="8">
-        <v>0</v>
-      </c>
-      <c r="F3" s="8">
-        <v>0</v>
-      </c>
-      <c r="G3" s="8">
-        <v>0</v>
-      </c>
-      <c r="H3" s="8">
-        <v>0</v>
-      </c>
-      <c r="I3" s="8">
-        <v>0</v>
-      </c>
-      <c r="J3" s="8">
-        <v>0</v>
-      </c>
-      <c r="K3" s="8">
-        <v>0</v>
-      </c>
-      <c r="L3" s="8">
-        <v>0</v>
-      </c>
-      <c r="M3" s="8">
-        <v>0</v>
-      </c>
-      <c r="N3" s="8">
-        <v>0</v>
-      </c>
-      <c r="O3" s="8">
-        <v>0</v>
-      </c>
-      <c r="P3" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="8">
-        <v>0</v>
-      </c>
-      <c r="R3" s="8">
-        <v>0</v>
-      </c>
-      <c r="S3" s="8">
-        <v>0</v>
-      </c>
-      <c r="T3" s="8">
-        <v>0</v>
-      </c>
-      <c r="U3" s="8">
-        <v>0</v>
-      </c>
-      <c r="V3" s="8">
-        <v>0</v>
-      </c>
-      <c r="W3" s="8">
-        <v>0</v>
-      </c>
-      <c r="X3" s="8">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="8">
-        <v>0</v>
-      </c>
-      <c r="Z3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AE3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AF3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AG3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AI3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AJ3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AK3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AL3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AM3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AN3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AO3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AP3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AQ3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AR3" s="8">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="P3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="R3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="S3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="T3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="U3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="V3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="W3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="X3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR3" s="9" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
+      <c r="A4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="M4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="N4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="O4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="P4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="R4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="S4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="T4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="U4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="V4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="W4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="X4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AP4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AQ4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AR4" s="9" t="s">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0</v>
+      </c>
+      <c r="F4" s="8">
+        <v>0</v>
+      </c>
+      <c r="G4" s="8">
+        <v>0</v>
+      </c>
+      <c r="H4" s="8">
+        <v>0</v>
+      </c>
+      <c r="I4" s="8">
+        <v>0</v>
+      </c>
+      <c r="J4" s="8">
+        <v>0</v>
+      </c>
+      <c r="K4" s="8">
+        <v>0</v>
+      </c>
+      <c r="L4" s="8">
+        <v>0</v>
+      </c>
+      <c r="M4" s="8">
+        <v>0</v>
+      </c>
+      <c r="N4" s="8">
+        <v>0</v>
+      </c>
+      <c r="O4" s="8">
+        <v>0</v>
+      </c>
+      <c r="P4" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>0</v>
+      </c>
+      <c r="R4" s="8">
+        <v>0</v>
+      </c>
+      <c r="S4" s="8">
+        <v>0</v>
+      </c>
+      <c r="T4" s="8">
+        <v>0</v>
+      </c>
+      <c r="U4" s="8">
+        <v>0</v>
+      </c>
+      <c r="V4" s="8">
+        <v>0</v>
+      </c>
+      <c r="W4" s="8">
+        <v>0</v>
+      </c>
+      <c r="X4" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AL4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AN4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AP4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AR4" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>14</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>2</v>
@@ -1215,10 +1210,10 @@
     </row>
     <row r="6" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>2</v>
@@ -1349,415 +1344,415 @@
     </row>
     <row r="7" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>5</v>
+        <v>11</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>6</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="8">
-        <v>0</v>
-      </c>
-      <c r="E7" s="8">
-        <v>0</v>
-      </c>
-      <c r="F7" s="8">
-        <v>0</v>
-      </c>
-      <c r="G7" s="8">
-        <v>0</v>
-      </c>
-      <c r="H7" s="8">
-        <v>0</v>
-      </c>
-      <c r="I7" s="8">
-        <v>0</v>
-      </c>
-      <c r="J7" s="8">
-        <v>0</v>
-      </c>
-      <c r="K7" s="8">
-        <v>0</v>
-      </c>
-      <c r="L7" s="8">
-        <v>0</v>
-      </c>
-      <c r="M7" s="8">
-        <v>0</v>
-      </c>
-      <c r="N7" s="8">
-        <v>0</v>
-      </c>
-      <c r="O7" s="8">
-        <v>0</v>
-      </c>
-      <c r="P7" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="8">
-        <v>0</v>
-      </c>
-      <c r="R7" s="8">
-        <v>0</v>
-      </c>
-      <c r="S7" s="8">
-        <v>0</v>
-      </c>
-      <c r="T7" s="8">
-        <v>0</v>
-      </c>
-      <c r="U7" s="8">
-        <v>0</v>
-      </c>
-      <c r="V7" s="8">
-        <v>0</v>
-      </c>
-      <c r="W7" s="8">
-        <v>0</v>
-      </c>
-      <c r="X7" s="8">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="8">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AJ7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AK7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AL7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AM7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AN7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AO7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AP7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AQ7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AR7" s="8">
+        <v>3</v>
+      </c>
+      <c r="D7" s="10">
+        <v>0</v>
+      </c>
+      <c r="E7" s="10">
+        <v>0</v>
+      </c>
+      <c r="F7" s="10">
+        <v>0</v>
+      </c>
+      <c r="G7" s="10">
+        <v>0</v>
+      </c>
+      <c r="H7" s="10">
+        <v>0</v>
+      </c>
+      <c r="I7" s="10">
+        <v>0</v>
+      </c>
+      <c r="J7" s="10">
+        <v>0</v>
+      </c>
+      <c r="K7" s="10">
+        <v>0</v>
+      </c>
+      <c r="L7" s="10">
+        <v>0</v>
+      </c>
+      <c r="M7" s="10">
+        <v>0</v>
+      </c>
+      <c r="N7" s="10">
+        <v>0</v>
+      </c>
+      <c r="O7" s="10">
+        <v>0</v>
+      </c>
+      <c r="P7" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="10">
+        <v>0</v>
+      </c>
+      <c r="R7" s="10">
+        <v>0</v>
+      </c>
+      <c r="S7" s="10">
+        <v>0</v>
+      </c>
+      <c r="T7" s="10">
+        <v>0</v>
+      </c>
+      <c r="U7" s="10">
+        <v>0</v>
+      </c>
+      <c r="V7" s="10">
+        <v>0</v>
+      </c>
+      <c r="W7" s="10">
+        <v>0</v>
+      </c>
+      <c r="X7" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR7" s="10">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>6</v>
+      <c r="A8" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>8</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="10">
-        <v>0</v>
-      </c>
-      <c r="E8" s="10">
-        <v>0</v>
-      </c>
-      <c r="F8" s="10">
-        <v>0</v>
-      </c>
-      <c r="G8" s="10">
-        <v>0</v>
-      </c>
-      <c r="H8" s="10">
-        <v>0</v>
-      </c>
-      <c r="I8" s="10">
-        <v>0</v>
-      </c>
-      <c r="J8" s="10">
-        <v>0</v>
-      </c>
-      <c r="K8" s="10">
-        <v>0</v>
-      </c>
-      <c r="L8" s="10">
-        <v>0</v>
-      </c>
-      <c r="M8" s="10">
-        <v>0</v>
-      </c>
-      <c r="N8" s="10">
-        <v>0</v>
-      </c>
-      <c r="O8" s="10">
-        <v>0</v>
-      </c>
-      <c r="P8" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="10">
-        <v>0</v>
-      </c>
-      <c r="R8" s="10">
-        <v>0</v>
-      </c>
-      <c r="S8" s="10">
-        <v>0</v>
-      </c>
-      <c r="T8" s="10">
-        <v>0</v>
-      </c>
-      <c r="U8" s="10">
-        <v>0</v>
-      </c>
-      <c r="V8" s="10">
-        <v>0</v>
-      </c>
-      <c r="W8" s="10">
-        <v>0</v>
-      </c>
-      <c r="X8" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AI8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AJ8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AK8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AL8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AN8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AO8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AP8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AQ8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AR8" s="10">
+        <v>9</v>
+      </c>
+      <c r="D8" s="8">
+        <v>0</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0</v>
+      </c>
+      <c r="F8" s="8">
+        <v>0</v>
+      </c>
+      <c r="G8" s="8">
+        <v>0</v>
+      </c>
+      <c r="H8" s="8">
+        <v>0</v>
+      </c>
+      <c r="I8" s="8">
+        <v>0</v>
+      </c>
+      <c r="J8" s="8">
+        <v>0</v>
+      </c>
+      <c r="K8" s="8">
+        <v>0</v>
+      </c>
+      <c r="L8" s="8">
+        <v>0</v>
+      </c>
+      <c r="M8" s="8">
+        <v>0</v>
+      </c>
+      <c r="N8" s="8">
+        <v>0</v>
+      </c>
+      <c r="O8" s="8">
+        <v>0</v>
+      </c>
+      <c r="P8" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>0</v>
+      </c>
+      <c r="R8" s="8">
+        <v>0</v>
+      </c>
+      <c r="S8" s="8">
+        <v>0</v>
+      </c>
+      <c r="T8" s="8">
+        <v>0</v>
+      </c>
+      <c r="U8" s="8">
+        <v>0</v>
+      </c>
+      <c r="V8" s="8">
+        <v>0</v>
+      </c>
+      <c r="W8" s="8">
+        <v>0</v>
+      </c>
+      <c r="X8" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AP8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AR8" s="8">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>8</v>
+      <c r="A9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>7</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="8">
-        <v>0</v>
-      </c>
-      <c r="E9" s="8">
-        <v>0</v>
-      </c>
-      <c r="F9" s="8">
-        <v>0</v>
-      </c>
-      <c r="G9" s="8">
-        <v>0</v>
-      </c>
-      <c r="H9" s="8">
-        <v>0</v>
-      </c>
-      <c r="I9" s="8">
-        <v>0</v>
-      </c>
-      <c r="J9" s="8">
-        <v>0</v>
-      </c>
-      <c r="K9" s="8">
-        <v>0</v>
-      </c>
-      <c r="L9" s="8">
-        <v>0</v>
-      </c>
-      <c r="M9" s="8">
-        <v>0</v>
-      </c>
-      <c r="N9" s="8">
-        <v>0</v>
-      </c>
-      <c r="O9" s="8">
-        <v>0</v>
-      </c>
-      <c r="P9" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>0</v>
-      </c>
-      <c r="R9" s="8">
-        <v>0</v>
-      </c>
-      <c r="S9" s="8">
-        <v>0</v>
-      </c>
-      <c r="T9" s="8">
-        <v>0</v>
-      </c>
-      <c r="U9" s="8">
-        <v>0</v>
-      </c>
-      <c r="V9" s="8">
-        <v>0</v>
-      </c>
-      <c r="W9" s="8">
-        <v>0</v>
-      </c>
-      <c r="X9" s="8">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="8">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="8">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="8">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="8">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="8">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="8">
-        <v>0</v>
-      </c>
-      <c r="AF9" s="8">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="8">
-        <v>0</v>
-      </c>
-      <c r="AH9" s="8">
-        <v>0</v>
-      </c>
-      <c r="AI9" s="8">
-        <v>0</v>
-      </c>
-      <c r="AJ9" s="8">
-        <v>0</v>
-      </c>
-      <c r="AK9" s="8">
-        <v>0</v>
-      </c>
-      <c r="AL9" s="8">
-        <v>0</v>
-      </c>
-      <c r="AM9" s="8">
-        <v>0</v>
-      </c>
-      <c r="AN9" s="8">
-        <v>0</v>
-      </c>
-      <c r="AO9" s="8">
-        <v>0</v>
-      </c>
-      <c r="AP9" s="8">
-        <v>0</v>
-      </c>
-      <c r="AQ9" s="8">
-        <v>0</v>
-      </c>
-      <c r="AR9" s="8">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="P9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="R9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="S9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="T9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="U9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="V9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="W9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="X9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR9" s="9" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>9</v>
+      <c r="A10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D10" s="8">
         <v>0</v>
@@ -1884,145 +1879,145 @@
       </c>
     </row>
     <row r="11" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>7</v>
+      <c r="A11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="K11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="M11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="N11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="O11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="P11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="R11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="S11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="T11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="U11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="V11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="W11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="X11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AP11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AQ11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AR11" s="9" t="s">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="D11" s="8">
+        <v>0</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0</v>
+      </c>
+      <c r="F11" s="8">
+        <v>0</v>
+      </c>
+      <c r="G11" s="8">
+        <v>0</v>
+      </c>
+      <c r="H11" s="8">
+        <v>0</v>
+      </c>
+      <c r="I11" s="8">
+        <v>0</v>
+      </c>
+      <c r="J11" s="8">
+        <v>0</v>
+      </c>
+      <c r="K11" s="8">
+        <v>0</v>
+      </c>
+      <c r="L11" s="8">
+        <v>0</v>
+      </c>
+      <c r="M11" s="8">
+        <v>0</v>
+      </c>
+      <c r="N11" s="8">
+        <v>0</v>
+      </c>
+      <c r="O11" s="8">
+        <v>0</v>
+      </c>
+      <c r="P11" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>0</v>
+      </c>
+      <c r="R11" s="8">
+        <v>0</v>
+      </c>
+      <c r="S11" s="8">
+        <v>0</v>
+      </c>
+      <c r="T11" s="8">
+        <v>0</v>
+      </c>
+      <c r="U11" s="8">
+        <v>0</v>
+      </c>
+      <c r="V11" s="8">
+        <v>0</v>
+      </c>
+      <c r="W11" s="8">
+        <v>0</v>
+      </c>
+      <c r="X11" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AL11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AN11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AP11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AR11" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="2" t="s">
         <v>14</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>2</v>
@@ -2153,403 +2148,135 @@
     </row>
     <row r="13" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>6</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D13" s="8">
-        <v>0</v>
-      </c>
-      <c r="E13" s="8">
-        <v>0</v>
-      </c>
-      <c r="F13" s="8">
-        <v>0</v>
-      </c>
-      <c r="G13" s="8">
-        <v>0</v>
-      </c>
-      <c r="H13" s="8">
-        <v>0</v>
-      </c>
-      <c r="I13" s="8">
-        <v>0</v>
-      </c>
-      <c r="J13" s="8">
-        <v>0</v>
-      </c>
-      <c r="K13" s="8">
-        <v>0</v>
-      </c>
-      <c r="L13" s="8">
-        <v>0</v>
-      </c>
-      <c r="M13" s="8">
-        <v>0</v>
-      </c>
-      <c r="N13" s="8">
-        <v>0</v>
-      </c>
-      <c r="O13" s="8">
-        <v>0</v>
-      </c>
-      <c r="P13" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="8">
-        <v>0</v>
-      </c>
-      <c r="R13" s="8">
-        <v>0</v>
-      </c>
-      <c r="S13" s="8">
-        <v>0</v>
-      </c>
-      <c r="T13" s="8">
-        <v>0</v>
-      </c>
-      <c r="U13" s="8">
-        <v>0</v>
-      </c>
-      <c r="V13" s="8">
-        <v>0</v>
-      </c>
-      <c r="W13" s="8">
-        <v>0</v>
-      </c>
-      <c r="X13" s="8">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="8">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="8">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="8">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC13" s="8">
-        <v>0</v>
-      </c>
-      <c r="AD13" s="8">
-        <v>0</v>
-      </c>
-      <c r="AE13" s="8">
-        <v>0</v>
-      </c>
-      <c r="AF13" s="8">
-        <v>0</v>
-      </c>
-      <c r="AG13" s="8">
-        <v>0</v>
-      </c>
-      <c r="AH13" s="8">
-        <v>0</v>
-      </c>
-      <c r="AI13" s="8">
-        <v>0</v>
-      </c>
-      <c r="AJ13" s="8">
-        <v>0</v>
-      </c>
-      <c r="AK13" s="8">
-        <v>0</v>
-      </c>
-      <c r="AL13" s="8">
-        <v>0</v>
-      </c>
-      <c r="AM13" s="8">
-        <v>0</v>
-      </c>
-      <c r="AN13" s="8">
-        <v>0</v>
-      </c>
-      <c r="AO13" s="8">
-        <v>0</v>
-      </c>
-      <c r="AP13" s="8">
-        <v>0</v>
-      </c>
-      <c r="AQ13" s="8">
-        <v>0</v>
-      </c>
-      <c r="AR13" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D14" s="8">
-        <v>0</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0</v>
-      </c>
-      <c r="F14" s="8">
-        <v>0</v>
-      </c>
-      <c r="G14" s="8">
-        <v>0</v>
-      </c>
-      <c r="H14" s="8">
-        <v>0</v>
-      </c>
-      <c r="I14" s="8">
-        <v>0</v>
-      </c>
-      <c r="J14" s="8">
-        <v>0</v>
-      </c>
-      <c r="K14" s="8">
-        <v>0</v>
-      </c>
-      <c r="L14" s="8">
-        <v>0</v>
-      </c>
-      <c r="M14" s="8">
-        <v>0</v>
-      </c>
-      <c r="N14" s="8">
-        <v>0</v>
-      </c>
-      <c r="O14" s="8">
-        <v>0</v>
-      </c>
-      <c r="P14" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="8">
-        <v>0</v>
-      </c>
-      <c r="R14" s="8">
-        <v>0</v>
-      </c>
-      <c r="S14" s="8">
-        <v>0</v>
-      </c>
-      <c r="T14" s="8">
-        <v>0</v>
-      </c>
-      <c r="U14" s="8">
-        <v>0</v>
-      </c>
-      <c r="V14" s="8">
-        <v>0</v>
-      </c>
-      <c r="W14" s="8">
-        <v>0</v>
-      </c>
-      <c r="X14" s="8">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="8">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="8">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="8">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="8">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="8">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="8">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="8">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="8">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="8">
-        <v>0</v>
-      </c>
-      <c r="AI14" s="8">
-        <v>0</v>
-      </c>
-      <c r="AJ14" s="8">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="8">
-        <v>0</v>
-      </c>
-      <c r="AL14" s="8">
-        <v>0</v>
-      </c>
-      <c r="AM14" s="8">
-        <v>0</v>
-      </c>
-      <c r="AN14" s="8">
-        <v>0</v>
-      </c>
-      <c r="AO14" s="8">
-        <v>0</v>
-      </c>
-      <c r="AP14" s="8">
-        <v>0</v>
-      </c>
-      <c r="AQ14" s="8">
-        <v>0</v>
-      </c>
-      <c r="AR14" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="10">
-        <v>0</v>
-      </c>
-      <c r="E15" s="10">
-        <v>0</v>
-      </c>
-      <c r="F15" s="10">
-        <v>0</v>
-      </c>
-      <c r="G15" s="10">
-        <v>0</v>
-      </c>
-      <c r="H15" s="10">
-        <v>0</v>
-      </c>
-      <c r="I15" s="10">
-        <v>0</v>
-      </c>
-      <c r="J15" s="10">
-        <v>0</v>
-      </c>
-      <c r="K15" s="10">
-        <v>0</v>
-      </c>
-      <c r="L15" s="10">
-        <v>0</v>
-      </c>
-      <c r="M15" s="10">
-        <v>0</v>
-      </c>
-      <c r="N15" s="10">
-        <v>0</v>
-      </c>
-      <c r="O15" s="10">
-        <v>0</v>
-      </c>
-      <c r="P15" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="10">
-        <v>0</v>
-      </c>
-      <c r="R15" s="10">
-        <v>0</v>
-      </c>
-      <c r="S15" s="10">
-        <v>0</v>
-      </c>
-      <c r="T15" s="10">
-        <v>0</v>
-      </c>
-      <c r="U15" s="10">
-        <v>0</v>
-      </c>
-      <c r="V15" s="10">
-        <v>0</v>
-      </c>
-      <c r="W15" s="10">
-        <v>0</v>
-      </c>
-      <c r="X15" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AG15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AH15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AI15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AJ15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AK15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AL15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AN15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AO15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AP15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AQ15" s="10">
-        <v>0</v>
-      </c>
-      <c r="AR15" s="10">
+      <c r="D13" s="10">
+        <v>0</v>
+      </c>
+      <c r="E13" s="10">
+        <v>0</v>
+      </c>
+      <c r="F13" s="10">
+        <v>0</v>
+      </c>
+      <c r="G13" s="10">
+        <v>0</v>
+      </c>
+      <c r="H13" s="10">
+        <v>0</v>
+      </c>
+      <c r="I13" s="10">
+        <v>0</v>
+      </c>
+      <c r="J13" s="10">
+        <v>0</v>
+      </c>
+      <c r="K13" s="10">
+        <v>0</v>
+      </c>
+      <c r="L13" s="10">
+        <v>0</v>
+      </c>
+      <c r="M13" s="10">
+        <v>0</v>
+      </c>
+      <c r="N13" s="10">
+        <v>0</v>
+      </c>
+      <c r="O13" s="10">
+        <v>0</v>
+      </c>
+      <c r="P13" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="10">
+        <v>0</v>
+      </c>
+      <c r="R13" s="10">
+        <v>0</v>
+      </c>
+      <c r="S13" s="10">
+        <v>0</v>
+      </c>
+      <c r="T13" s="10">
+        <v>0</v>
+      </c>
+      <c r="U13" s="10">
+        <v>0</v>
+      </c>
+      <c r="V13" s="10">
+        <v>0</v>
+      </c>
+      <c r="W13" s="10">
+        <v>0</v>
+      </c>
+      <c r="X13" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR13" s="10">
         <v>0</v>
       </c>
     </row>
@@ -2561,7 +2288,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:AQ8"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.81640625" customWidth="1"/>
@@ -2703,7 +2430,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2" s="8">
         <v>0</v>
@@ -2830,270 +2557,270 @@
       </c>
     </row>
     <row r="3" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="12" t="s">
-        <v>9</v>
+      <c r="A3" s="7" t="s">
+        <v>7</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0</v>
-      </c>
-      <c r="D3" s="8">
-        <v>0</v>
-      </c>
-      <c r="E3" s="8">
-        <v>0</v>
-      </c>
-      <c r="F3" s="8">
-        <v>0</v>
-      </c>
-      <c r="G3" s="8">
-        <v>0</v>
-      </c>
-      <c r="H3" s="8">
-        <v>0</v>
-      </c>
-      <c r="I3" s="8">
-        <v>0</v>
-      </c>
-      <c r="J3" s="8">
-        <v>0</v>
-      </c>
-      <c r="K3" s="8">
-        <v>0</v>
-      </c>
-      <c r="L3" s="8">
-        <v>0</v>
-      </c>
-      <c r="M3" s="8">
-        <v>0</v>
-      </c>
-      <c r="N3" s="8">
-        <v>0</v>
-      </c>
-      <c r="O3" s="8">
-        <v>0</v>
-      </c>
-      <c r="P3" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="8">
-        <v>0</v>
-      </c>
-      <c r="R3" s="8">
-        <v>0</v>
-      </c>
-      <c r="S3" s="8">
-        <v>0</v>
-      </c>
-      <c r="T3" s="8">
-        <v>0</v>
-      </c>
-      <c r="U3" s="8">
-        <v>0</v>
-      </c>
-      <c r="V3" s="8">
-        <v>0</v>
-      </c>
-      <c r="W3" s="8">
-        <v>0</v>
-      </c>
-      <c r="X3" s="8">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="8">
-        <v>0</v>
-      </c>
-      <c r="Z3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AE3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AF3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AG3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AI3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AJ3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AK3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AL3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AM3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AN3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AO3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AP3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AQ3" s="8">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="P3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="R3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="S3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="T3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="U3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="V3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="W3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="X3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ3" s="9" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
-        <v>7</v>
+      <c r="A4" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="M4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="N4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="O4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="P4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="R4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="S4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="T4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="U4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="V4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="W4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="X4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AC4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AF4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AG4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AH4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AL4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AM4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AP4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="AQ4" s="9" t="s">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0</v>
+      </c>
+      <c r="F4" s="8">
+        <v>0</v>
+      </c>
+      <c r="G4" s="8">
+        <v>0</v>
+      </c>
+      <c r="H4" s="8">
+        <v>0</v>
+      </c>
+      <c r="I4" s="8">
+        <v>0</v>
+      </c>
+      <c r="J4" s="8">
+        <v>0</v>
+      </c>
+      <c r="K4" s="8">
+        <v>0</v>
+      </c>
+      <c r="L4" s="8">
+        <v>0</v>
+      </c>
+      <c r="M4" s="8">
+        <v>0</v>
+      </c>
+      <c r="N4" s="8">
+        <v>0</v>
+      </c>
+      <c r="O4" s="8">
+        <v>0</v>
+      </c>
+      <c r="P4" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>0</v>
+      </c>
+      <c r="R4" s="8">
+        <v>0</v>
+      </c>
+      <c r="S4" s="8">
+        <v>0</v>
+      </c>
+      <c r="T4" s="8">
+        <v>0</v>
+      </c>
+      <c r="U4" s="8">
+        <v>0</v>
+      </c>
+      <c r="V4" s="8">
+        <v>0</v>
+      </c>
+      <c r="W4" s="8">
+        <v>0</v>
+      </c>
+      <c r="X4" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AL4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AN4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AP4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="8">
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>2</v>
@@ -3223,8 +2950,8 @@
       </c>
     </row>
     <row r="6" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>15</v>
+      <c r="A6" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>2</v>
@@ -3355,263 +3082,132 @@
     </row>
     <row r="7" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="8">
-        <v>0</v>
-      </c>
-      <c r="D7" s="8">
-        <v>0</v>
-      </c>
-      <c r="E7" s="8">
-        <v>0</v>
-      </c>
-      <c r="F7" s="8">
-        <v>0</v>
-      </c>
-      <c r="G7" s="8">
-        <v>0</v>
-      </c>
-      <c r="H7" s="8">
-        <v>0</v>
-      </c>
-      <c r="I7" s="8">
-        <v>0</v>
-      </c>
-      <c r="J7" s="8">
-        <v>0</v>
-      </c>
-      <c r="K7" s="8">
-        <v>0</v>
-      </c>
-      <c r="L7" s="8">
-        <v>0</v>
-      </c>
-      <c r="M7" s="8">
-        <v>0</v>
-      </c>
-      <c r="N7" s="8">
-        <v>0</v>
-      </c>
-      <c r="O7" s="8">
-        <v>0</v>
-      </c>
-      <c r="P7" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="8">
-        <v>0</v>
-      </c>
-      <c r="R7" s="8">
-        <v>0</v>
-      </c>
-      <c r="S7" s="8">
-        <v>0</v>
-      </c>
-      <c r="T7" s="8">
-        <v>0</v>
-      </c>
-      <c r="U7" s="8">
-        <v>0</v>
-      </c>
-      <c r="V7" s="8">
-        <v>0</v>
-      </c>
-      <c r="W7" s="8">
-        <v>0</v>
-      </c>
-      <c r="X7" s="8">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="8">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AJ7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AK7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AL7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AM7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AN7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AO7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AP7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AQ7" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="10">
-        <v>0</v>
-      </c>
-      <c r="D8" s="10">
-        <v>0</v>
-      </c>
-      <c r="E8" s="10">
-        <v>0</v>
-      </c>
-      <c r="F8" s="10">
-        <v>0</v>
-      </c>
-      <c r="G8" s="10">
-        <v>0</v>
-      </c>
-      <c r="H8" s="10">
-        <v>0</v>
-      </c>
-      <c r="I8" s="10">
-        <v>0</v>
-      </c>
-      <c r="J8" s="10">
-        <v>0</v>
-      </c>
-      <c r="K8" s="10">
-        <v>0</v>
-      </c>
-      <c r="L8" s="10">
-        <v>0</v>
-      </c>
-      <c r="M8" s="10">
-        <v>0</v>
-      </c>
-      <c r="N8" s="10">
-        <v>0</v>
-      </c>
-      <c r="O8" s="10">
-        <v>0</v>
-      </c>
-      <c r="P8" s="10">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="10">
-        <v>0</v>
-      </c>
-      <c r="R8" s="10">
-        <v>0</v>
-      </c>
-      <c r="S8" s="10">
-        <v>0</v>
-      </c>
-      <c r="T8" s="10">
-        <v>0</v>
-      </c>
-      <c r="U8" s="10">
-        <v>0</v>
-      </c>
-      <c r="V8" s="10">
-        <v>0</v>
-      </c>
-      <c r="W8" s="10">
-        <v>0</v>
-      </c>
-      <c r="X8" s="10">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="10">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AC8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AI8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AJ8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AK8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AL8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AM8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AN8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AO8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AP8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AQ8" s="10">
+      <c r="C7" s="10">
+        <v>0</v>
+      </c>
+      <c r="D7" s="10">
+        <v>0</v>
+      </c>
+      <c r="E7" s="10">
+        <v>0</v>
+      </c>
+      <c r="F7" s="10">
+        <v>0</v>
+      </c>
+      <c r="G7" s="10">
+        <v>0</v>
+      </c>
+      <c r="H7" s="10">
+        <v>0</v>
+      </c>
+      <c r="I7" s="10">
+        <v>0</v>
+      </c>
+      <c r="J7" s="10">
+        <v>0</v>
+      </c>
+      <c r="K7" s="10">
+        <v>0</v>
+      </c>
+      <c r="L7" s="10">
+        <v>0</v>
+      </c>
+      <c r="M7" s="10">
+        <v>0</v>
+      </c>
+      <c r="N7" s="10">
+        <v>0</v>
+      </c>
+      <c r="O7" s="10">
+        <v>0</v>
+      </c>
+      <c r="P7" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="10">
+        <v>0</v>
+      </c>
+      <c r="R7" s="10">
+        <v>0</v>
+      </c>
+      <c r="S7" s="10">
+        <v>0</v>
+      </c>
+      <c r="T7" s="10">
+        <v>0</v>
+      </c>
+      <c r="U7" s="10">
+        <v>0</v>
+      </c>
+      <c r="V7" s="10">
+        <v>0</v>
+      </c>
+      <c r="W7" s="10">
+        <v>0</v>
+      </c>
+      <c r="X7" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="10">
         <v>0</v>
       </c>
     </row>

--- a/backend/Rwanda/technoeconomic-inputs-{model}.xlsx
+++ b/backend/Rwanda/technoeconomic-inputs-{model}.xlsx
@@ -5,16 +5,17 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/{templates}/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/Rwanda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="6_{0E28AF21-1CE2-4A91-9061-FE1E52D24DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEA536E1-4A58-4C9B-AB49-7F993DF01835}"/>
+  <xr:revisionPtr revIDLastSave="50" documentId="6_{0E28AF21-1CE2-4A91-9061-FE1E52D24DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{508A030D-D837-4055-AF9A-98FC29687139}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Electricity" sheetId="2" r:id="rId1"/>
-    <sheet name="LPG" sheetId="1" r:id="rId2"/>
+    <sheet name="Electricity &amp; E-Cooking" sheetId="3" r:id="rId1"/>
+    <sheet name="Electricity (Low access)" sheetId="2" r:id="rId2"/>
+    <sheet name="LPG" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029" iterate="1"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="16">
   <si>
     <t>Units</t>
   </si>
@@ -529,6 +530,1762 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D8C45DF-8420-4110-B27F-387B05C144F7}">
+  <dimension ref="A1:AR13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.54296875" customWidth="1"/>
+    <col min="2" max="2" width="25.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="4">
+        <v>2020</v>
+      </c>
+      <c r="E1" s="4">
+        <v>2021</v>
+      </c>
+      <c r="F1" s="4">
+        <v>2022</v>
+      </c>
+      <c r="G1" s="4">
+        <v>2023</v>
+      </c>
+      <c r="H1" s="4">
+        <v>2024</v>
+      </c>
+      <c r="I1" s="4">
+        <v>2025</v>
+      </c>
+      <c r="J1" s="4">
+        <v>2026</v>
+      </c>
+      <c r="K1" s="4">
+        <v>2027</v>
+      </c>
+      <c r="L1" s="4">
+        <v>2028</v>
+      </c>
+      <c r="M1" s="4">
+        <v>2029</v>
+      </c>
+      <c r="N1" s="4">
+        <v>2030</v>
+      </c>
+      <c r="O1" s="4">
+        <v>2031</v>
+      </c>
+      <c r="P1" s="4">
+        <v>2032</v>
+      </c>
+      <c r="Q1" s="4">
+        <v>2033</v>
+      </c>
+      <c r="R1" s="4">
+        <v>2034</v>
+      </c>
+      <c r="S1" s="4">
+        <v>2035</v>
+      </c>
+      <c r="T1" s="4">
+        <v>2036</v>
+      </c>
+      <c r="U1" s="4">
+        <v>2037</v>
+      </c>
+      <c r="V1" s="4">
+        <v>2038</v>
+      </c>
+      <c r="W1" s="4">
+        <v>2039</v>
+      </c>
+      <c r="X1" s="4">
+        <v>2040</v>
+      </c>
+      <c r="Y1" s="4">
+        <v>2041</v>
+      </c>
+      <c r="Z1" s="4">
+        <v>2042</v>
+      </c>
+      <c r="AA1" s="4">
+        <v>2043</v>
+      </c>
+      <c r="AB1" s="4">
+        <v>2044</v>
+      </c>
+      <c r="AC1" s="4">
+        <v>2045</v>
+      </c>
+      <c r="AD1" s="4">
+        <v>2046</v>
+      </c>
+      <c r="AE1" s="4">
+        <v>2047</v>
+      </c>
+      <c r="AF1" s="4">
+        <v>2048</v>
+      </c>
+      <c r="AG1" s="4">
+        <v>2049</v>
+      </c>
+      <c r="AH1" s="4">
+        <v>2050</v>
+      </c>
+      <c r="AI1" s="4">
+        <v>2051</v>
+      </c>
+      <c r="AJ1" s="4">
+        <v>2052</v>
+      </c>
+      <c r="AK1" s="4">
+        <v>2053</v>
+      </c>
+      <c r="AL1" s="4">
+        <v>2054</v>
+      </c>
+      <c r="AM1" s="4">
+        <v>2055</v>
+      </c>
+      <c r="AN1" s="4">
+        <v>2056</v>
+      </c>
+      <c r="AO1" s="4">
+        <v>2057</v>
+      </c>
+      <c r="AP1" s="4">
+        <v>2058</v>
+      </c>
+      <c r="AQ1" s="4">
+        <v>2059</v>
+      </c>
+      <c r="AR1" s="4">
+        <v>2060</v>
+      </c>
+    </row>
+    <row r="2" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="8">
+        <v>0</v>
+      </c>
+      <c r="E2" s="8">
+        <v>0</v>
+      </c>
+      <c r="F2" s="8">
+        <v>0</v>
+      </c>
+      <c r="G2" s="8">
+        <v>0</v>
+      </c>
+      <c r="H2" s="8">
+        <v>0</v>
+      </c>
+      <c r="I2" s="8">
+        <v>0</v>
+      </c>
+      <c r="J2" s="8">
+        <v>0</v>
+      </c>
+      <c r="K2" s="8">
+        <v>0</v>
+      </c>
+      <c r="L2" s="8">
+        <v>0</v>
+      </c>
+      <c r="M2" s="8">
+        <v>0</v>
+      </c>
+      <c r="N2" s="8">
+        <v>0</v>
+      </c>
+      <c r="O2" s="8">
+        <v>0</v>
+      </c>
+      <c r="P2" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>0</v>
+      </c>
+      <c r="R2" s="8">
+        <v>0</v>
+      </c>
+      <c r="S2" s="8">
+        <v>0</v>
+      </c>
+      <c r="T2" s="8">
+        <v>0</v>
+      </c>
+      <c r="U2" s="8">
+        <v>0</v>
+      </c>
+      <c r="V2" s="8">
+        <v>0</v>
+      </c>
+      <c r="W2" s="8">
+        <v>0</v>
+      </c>
+      <c r="X2" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AH2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AK2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AL2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AN2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AP2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AR2" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="P3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="R3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="S3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="T3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="U3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="V3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="W3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="X3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR3" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="8">
+        <v>0</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0</v>
+      </c>
+      <c r="F4" s="8">
+        <v>0</v>
+      </c>
+      <c r="G4" s="8">
+        <v>0</v>
+      </c>
+      <c r="H4" s="8">
+        <v>0</v>
+      </c>
+      <c r="I4" s="8">
+        <v>0</v>
+      </c>
+      <c r="J4" s="8">
+        <v>0</v>
+      </c>
+      <c r="K4" s="8">
+        <v>0</v>
+      </c>
+      <c r="L4" s="8">
+        <v>0</v>
+      </c>
+      <c r="M4" s="8">
+        <v>0</v>
+      </c>
+      <c r="N4" s="8">
+        <v>0</v>
+      </c>
+      <c r="O4" s="8">
+        <v>0</v>
+      </c>
+      <c r="P4" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>0</v>
+      </c>
+      <c r="R4" s="8">
+        <v>0</v>
+      </c>
+      <c r="S4" s="8">
+        <v>0</v>
+      </c>
+      <c r="T4" s="8">
+        <v>0</v>
+      </c>
+      <c r="U4" s="8">
+        <v>0</v>
+      </c>
+      <c r="V4" s="8">
+        <v>0</v>
+      </c>
+      <c r="W4" s="8">
+        <v>0</v>
+      </c>
+      <c r="X4" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AL4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AN4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AP4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AR4" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="8">
+        <v>0</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0</v>
+      </c>
+      <c r="F5" s="8">
+        <v>0</v>
+      </c>
+      <c r="G5" s="8">
+        <v>0</v>
+      </c>
+      <c r="H5" s="8">
+        <v>0</v>
+      </c>
+      <c r="I5" s="8">
+        <v>0</v>
+      </c>
+      <c r="J5" s="8">
+        <v>0</v>
+      </c>
+      <c r="K5" s="8">
+        <v>0</v>
+      </c>
+      <c r="L5" s="8">
+        <v>0</v>
+      </c>
+      <c r="M5" s="8">
+        <v>0</v>
+      </c>
+      <c r="N5" s="8">
+        <v>0</v>
+      </c>
+      <c r="O5" s="8">
+        <v>0</v>
+      </c>
+      <c r="P5" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>0</v>
+      </c>
+      <c r="R5" s="8">
+        <v>0</v>
+      </c>
+      <c r="S5" s="8">
+        <v>0</v>
+      </c>
+      <c r="T5" s="8">
+        <v>0</v>
+      </c>
+      <c r="U5" s="8">
+        <v>0</v>
+      </c>
+      <c r="V5" s="8">
+        <v>0</v>
+      </c>
+      <c r="W5" s="8">
+        <v>0</v>
+      </c>
+      <c r="X5" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AL5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AN5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AP5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="8">
+        <v>0</v>
+      </c>
+      <c r="AR5" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="8">
+        <v>0</v>
+      </c>
+      <c r="E6" s="8">
+        <v>0</v>
+      </c>
+      <c r="F6" s="8">
+        <v>0</v>
+      </c>
+      <c r="G6" s="8">
+        <v>0</v>
+      </c>
+      <c r="H6" s="8">
+        <v>0</v>
+      </c>
+      <c r="I6" s="8">
+        <v>0</v>
+      </c>
+      <c r="J6" s="8">
+        <v>0</v>
+      </c>
+      <c r="K6" s="8">
+        <v>0</v>
+      </c>
+      <c r="L6" s="8">
+        <v>0</v>
+      </c>
+      <c r="M6" s="8">
+        <v>0</v>
+      </c>
+      <c r="N6" s="8">
+        <v>0</v>
+      </c>
+      <c r="O6" s="8">
+        <v>0</v>
+      </c>
+      <c r="P6" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>0</v>
+      </c>
+      <c r="R6" s="8">
+        <v>0</v>
+      </c>
+      <c r="S6" s="8">
+        <v>0</v>
+      </c>
+      <c r="T6" s="8">
+        <v>0</v>
+      </c>
+      <c r="U6" s="8">
+        <v>0</v>
+      </c>
+      <c r="V6" s="8">
+        <v>0</v>
+      </c>
+      <c r="W6" s="8">
+        <v>0</v>
+      </c>
+      <c r="X6" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AP6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="8">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="10">
+        <v>0</v>
+      </c>
+      <c r="E7" s="10">
+        <v>0</v>
+      </c>
+      <c r="F7" s="10">
+        <v>0</v>
+      </c>
+      <c r="G7" s="10">
+        <v>0</v>
+      </c>
+      <c r="H7" s="10">
+        <v>0</v>
+      </c>
+      <c r="I7" s="10">
+        <v>0</v>
+      </c>
+      <c r="J7" s="10">
+        <v>0</v>
+      </c>
+      <c r="K7" s="10">
+        <v>0</v>
+      </c>
+      <c r="L7" s="10">
+        <v>0</v>
+      </c>
+      <c r="M7" s="10">
+        <v>0</v>
+      </c>
+      <c r="N7" s="10">
+        <v>0</v>
+      </c>
+      <c r="O7" s="10">
+        <v>0</v>
+      </c>
+      <c r="P7" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="10">
+        <v>0</v>
+      </c>
+      <c r="R7" s="10">
+        <v>0</v>
+      </c>
+      <c r="S7" s="10">
+        <v>0</v>
+      </c>
+      <c r="T7" s="10">
+        <v>0</v>
+      </c>
+      <c r="U7" s="10">
+        <v>0</v>
+      </c>
+      <c r="V7" s="10">
+        <v>0</v>
+      </c>
+      <c r="W7" s="10">
+        <v>0</v>
+      </c>
+      <c r="X7" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR7" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="8">
+        <v>0</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0</v>
+      </c>
+      <c r="F8" s="8">
+        <v>0</v>
+      </c>
+      <c r="G8" s="8">
+        <v>0</v>
+      </c>
+      <c r="H8" s="8">
+        <v>0</v>
+      </c>
+      <c r="I8" s="8">
+        <v>0</v>
+      </c>
+      <c r="J8" s="8">
+        <v>0</v>
+      </c>
+      <c r="K8" s="8">
+        <v>0</v>
+      </c>
+      <c r="L8" s="8">
+        <v>0</v>
+      </c>
+      <c r="M8" s="8">
+        <v>0</v>
+      </c>
+      <c r="N8" s="8">
+        <v>0</v>
+      </c>
+      <c r="O8" s="8">
+        <v>0</v>
+      </c>
+      <c r="P8" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>0</v>
+      </c>
+      <c r="R8" s="8">
+        <v>0</v>
+      </c>
+      <c r="S8" s="8">
+        <v>0</v>
+      </c>
+      <c r="T8" s="8">
+        <v>0</v>
+      </c>
+      <c r="U8" s="8">
+        <v>0</v>
+      </c>
+      <c r="V8" s="8">
+        <v>0</v>
+      </c>
+      <c r="W8" s="8">
+        <v>0</v>
+      </c>
+      <c r="X8" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AP8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="8">
+        <v>0</v>
+      </c>
+      <c r="AR8" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="P9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="R9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="S9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="T9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="U9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="V9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="W9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="X9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AC9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AG9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AH9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AL9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AM9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AQ9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="AR9" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="8">
+        <v>0</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0</v>
+      </c>
+      <c r="F10" s="8">
+        <v>0</v>
+      </c>
+      <c r="G10" s="8">
+        <v>0</v>
+      </c>
+      <c r="H10" s="8">
+        <v>0</v>
+      </c>
+      <c r="I10" s="8">
+        <v>0</v>
+      </c>
+      <c r="J10" s="8">
+        <v>0</v>
+      </c>
+      <c r="K10" s="8">
+        <v>0</v>
+      </c>
+      <c r="L10" s="8">
+        <v>0</v>
+      </c>
+      <c r="M10" s="8">
+        <v>0</v>
+      </c>
+      <c r="N10" s="8">
+        <v>0</v>
+      </c>
+      <c r="O10" s="8">
+        <v>0</v>
+      </c>
+      <c r="P10" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="8">
+        <v>0</v>
+      </c>
+      <c r="R10" s="8">
+        <v>0</v>
+      </c>
+      <c r="S10" s="8">
+        <v>0</v>
+      </c>
+      <c r="T10" s="8">
+        <v>0</v>
+      </c>
+      <c r="U10" s="8">
+        <v>0</v>
+      </c>
+      <c r="V10" s="8">
+        <v>0</v>
+      </c>
+      <c r="W10" s="8">
+        <v>0</v>
+      </c>
+      <c r="X10" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AL10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AN10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AP10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="8">
+        <v>0</v>
+      </c>
+      <c r="AR10" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="8">
+        <v>0</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0</v>
+      </c>
+      <c r="F11" s="8">
+        <v>0</v>
+      </c>
+      <c r="G11" s="8">
+        <v>0</v>
+      </c>
+      <c r="H11" s="8">
+        <v>0</v>
+      </c>
+      <c r="I11" s="8">
+        <v>0</v>
+      </c>
+      <c r="J11" s="8">
+        <v>0</v>
+      </c>
+      <c r="K11" s="8">
+        <v>0</v>
+      </c>
+      <c r="L11" s="8">
+        <v>0</v>
+      </c>
+      <c r="M11" s="8">
+        <v>0</v>
+      </c>
+      <c r="N11" s="8">
+        <v>0</v>
+      </c>
+      <c r="O11" s="8">
+        <v>0</v>
+      </c>
+      <c r="P11" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>0</v>
+      </c>
+      <c r="R11" s="8">
+        <v>0</v>
+      </c>
+      <c r="S11" s="8">
+        <v>0</v>
+      </c>
+      <c r="T11" s="8">
+        <v>0</v>
+      </c>
+      <c r="U11" s="8">
+        <v>0</v>
+      </c>
+      <c r="V11" s="8">
+        <v>0</v>
+      </c>
+      <c r="W11" s="8">
+        <v>0</v>
+      </c>
+      <c r="X11" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AL11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AN11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AP11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AR11" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="8">
+        <v>0</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0</v>
+      </c>
+      <c r="F12" s="8">
+        <v>0</v>
+      </c>
+      <c r="G12" s="8">
+        <v>0</v>
+      </c>
+      <c r="H12" s="8">
+        <v>0</v>
+      </c>
+      <c r="I12" s="8">
+        <v>0</v>
+      </c>
+      <c r="J12" s="8">
+        <v>0</v>
+      </c>
+      <c r="K12" s="8">
+        <v>0</v>
+      </c>
+      <c r="L12" s="8">
+        <v>0</v>
+      </c>
+      <c r="M12" s="8">
+        <v>0</v>
+      </c>
+      <c r="N12" s="8">
+        <v>0</v>
+      </c>
+      <c r="O12" s="8">
+        <v>0</v>
+      </c>
+      <c r="P12" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="8">
+        <v>0</v>
+      </c>
+      <c r="R12" s="8">
+        <v>0</v>
+      </c>
+      <c r="S12" s="8">
+        <v>0</v>
+      </c>
+      <c r="T12" s="8">
+        <v>0</v>
+      </c>
+      <c r="U12" s="8">
+        <v>0</v>
+      </c>
+      <c r="V12" s="8">
+        <v>0</v>
+      </c>
+      <c r="W12" s="8">
+        <v>0</v>
+      </c>
+      <c r="X12" s="8">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="8">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="8">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="8">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="8">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="8">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="8">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="8">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="8">
+        <v>0</v>
+      </c>
+      <c r="AL12" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM12" s="8">
+        <v>0</v>
+      </c>
+      <c r="AN12" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO12" s="8">
+        <v>0</v>
+      </c>
+      <c r="AP12" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="8">
+        <v>0</v>
+      </c>
+      <c r="AR12" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="10">
+        <v>0</v>
+      </c>
+      <c r="E13" s="10">
+        <v>0</v>
+      </c>
+      <c r="F13" s="10">
+        <v>0</v>
+      </c>
+      <c r="G13" s="10">
+        <v>0</v>
+      </c>
+      <c r="H13" s="10">
+        <v>0</v>
+      </c>
+      <c r="I13" s="10">
+        <v>0</v>
+      </c>
+      <c r="J13" s="10">
+        <v>0</v>
+      </c>
+      <c r="K13" s="10">
+        <v>0</v>
+      </c>
+      <c r="L13" s="10">
+        <v>0</v>
+      </c>
+      <c r="M13" s="10">
+        <v>0</v>
+      </c>
+      <c r="N13" s="10">
+        <v>0</v>
+      </c>
+      <c r="O13" s="10">
+        <v>0</v>
+      </c>
+      <c r="P13" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="10">
+        <v>0</v>
+      </c>
+      <c r="R13" s="10">
+        <v>0</v>
+      </c>
+      <c r="S13" s="10">
+        <v>0</v>
+      </c>
+      <c r="T13" s="10">
+        <v>0</v>
+      </c>
+      <c r="U13" s="10">
+        <v>0</v>
+      </c>
+      <c r="V13" s="10">
+        <v>0</v>
+      </c>
+      <c r="W13" s="10">
+        <v>0</v>
+      </c>
+      <c r="X13" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="10">
+        <v>0</v>
+      </c>
+      <c r="AR13" s="10">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99682AE1-5334-4A99-9652-64DF807A4E7D}">
   <sheetPr codeName="Hoja2"/>
   <dimension ref="A1:AR13"/>
@@ -2285,7 +4042,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja1"/>
   <dimension ref="A1:AQ7"/>

--- a/backend/Rwanda/technoeconomic-inputs-{model}.xlsx
+++ b/backend/Rwanda/technoeconomic-inputs-{model}.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/Rwanda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="56" documentId="6_{0E28AF21-1CE2-4A91-9061-FE1E52D24DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7FDC795-9FD2-44E4-BA18-2AF3D5FB0B99}"/>
+  <xr:revisionPtr revIDLastSave="60" documentId="6_{0E28AF21-1CE2-4A91-9061-FE1E52D24DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B998A54-3DC8-4098-9C68-9C9532C7565B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,9 +64,6 @@
     <t>kWh</t>
   </si>
   <si>
-    <t>Type - Inputs</t>
-  </si>
-  <si>
     <t>GRID</t>
   </si>
   <si>
@@ -77,6 +74,9 @@
   </si>
   <si>
     <t>OFF-GRID</t>
+  </si>
+  <si>
+    <t>System</t>
   </si>
 </sst>
 </file>
@@ -239,6 +239,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -513,7 +517,7 @@
   <sheetData>
     <row r="1" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>1</v>
@@ -647,7 +651,7 @@
     </row>
     <row r="2" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>6</v>
@@ -781,10 +785,10 @@
     </row>
     <row r="3" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>2</v>
@@ -915,10 +919,10 @@
     </row>
     <row r="4" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>2</v>
@@ -1049,7 +1053,7 @@
     </row>
     <row r="5" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>4</v>
@@ -1183,7 +1187,7 @@
     </row>
     <row r="6" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>5</v>
@@ -1317,7 +1321,7 @@
     </row>
     <row r="7" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>6</v>
@@ -1451,10 +1455,10 @@
     </row>
     <row r="8" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>2</v>
@@ -1585,10 +1589,10 @@
     </row>
     <row r="9" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>2</v>
@@ -1719,7 +1723,7 @@
     </row>
     <row r="10" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>4</v>
@@ -1853,7 +1857,7 @@
     </row>
     <row r="11" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>5</v>
@@ -2002,7 +2006,7 @@
   <sheetData>
     <row r="1" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>1</v>
@@ -2136,7 +2140,7 @@
     </row>
     <row r="2" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>6</v>
@@ -2270,10 +2274,10 @@
     </row>
     <row r="3" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>2</v>
@@ -2404,10 +2408,10 @@
     </row>
     <row r="4" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>2</v>
@@ -2538,7 +2542,7 @@
     </row>
     <row r="5" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>4</v>
@@ -2672,7 +2676,7 @@
     </row>
     <row r="6" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>5</v>
@@ -2806,7 +2810,7 @@
     </row>
     <row r="7" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>6</v>
@@ -2940,10 +2944,10 @@
     </row>
     <row r="8" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>2</v>
@@ -3074,10 +3078,10 @@
     </row>
     <row r="9" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>2</v>
@@ -3208,7 +3212,7 @@
     </row>
     <row r="10" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>4</v>
@@ -3342,7 +3346,7 @@
     </row>
     <row r="11" spans="1:44" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>5</v>
@@ -3752,7 +3756,7 @@
     </row>
     <row r="3" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>2</v>
@@ -3883,7 +3887,7 @@
     </row>
     <row r="4" spans="1:43" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>2</v>
